--- a/ClosedXML.Tests/Resource/Examples/Misc/DataTypes.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Misc/DataTypes.xlsx
@@ -92,9 +92,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="164" formatCode="@"/>
   </x:numFmts>
   <x:fonts count="1">
     <x:font>
@@ -148,7 +147,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -173,7 +172,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
